--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_934_Egypt_Red_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_934_Egypt_Red_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R9a25a9cd1241483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rf485ec4c2a1d4938"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2043be3ff1ce4cdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3dfdffa770534d4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6eb55628b0f94b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R196701afa9304a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re679ae3ed391400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R51fdf919b5834507"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3ec662b0e8b749b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3a0a182a9201436b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R05ee3b7b31044f63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R132cd665e1dc43d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ934CommercialTable" displayName="EEZ934CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ934CommercialTable" displayName="EEZ934CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ934FunctionalTable" displayName="EEZ934FunctionalTable" ref="A1:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O16"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ934FunctionalTable" displayName="EEZ934FunctionalTable" ref="A1:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E16"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ934ValidationTable" displayName="EEZ934ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ934ValidationTable" displayName="EEZ934ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4513,7 +4467,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R342d2e89f1c2442c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23947a462a7148f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4523,20 +4477,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4544,606 +4488,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6706.76138556</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2496513862438827</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>177.68525350888848</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6706.76138556</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>177.69310681251017</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$58,A2,'Species'!$U$2:$U$58))</x:f>
-        <x:v>1191745.2672503318</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2496513862438827</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>177.68525350888848</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1191692.5970168528</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>52.67023347900249</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000441978355918</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.000044197835591872554</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1157.6048424599999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.402805045076436</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>252.81628486178803</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1157.6048424599999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>254.69547139719256</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$58,A3,'Species'!$U$2:$U$58))</x:f>
-        <x:v>294836.7110420225</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.402805045076436</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>252.81628486178803</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>292661.3556087526</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2175.3554332699277</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0074330122224202</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.007433012222420218</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>463.8561842</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.16</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1445.439770745928</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>463.8561842</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1445.439770745928</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$58,A4,'Species'!$U$2:$U$58))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>670476.1765491288</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.16</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1445.439770745928</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>670476.1765491288</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>9492.02115336</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.8103578288721787</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>64.61864230604662</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>9492.02115336</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>66.71944027223583</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$58,A5,'Species'!$U$2:$U$58))</x:f>
-        <x:v>633302.3384044016</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.8103578288721787</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>64.61864230604662</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>613361.519670398</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>19940.81873400358</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0325107103959166</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.03251071039591655</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
-        <x:v>1</x:v>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$58,A6,'Species'!$U$2:$U$58))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>11990.667320546</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6476036623831067</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>444.22568158766444</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>11990.667320546</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>852.7395597231907</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$58,A7,'Species'!$U$2:$U$58))</x:f>
-        <x:v>10224916.371709647</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6476036623831067</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>444.22568158766444</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>5326562.363160481</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4898354.008549166</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.919608872399038</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.9196088723990382</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>35062.162629466</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.643903288528622</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>440.45676885595907</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>35062.162629466</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>660.420991011108</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$58,A8,'Species'!$U$2:$U$58))</x:f>
-        <x:v>23155788.19074457</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.643903288528622</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>440.45676885595907</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>15443366.860876752</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>7712421.329867819</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.49940025380126</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4994002538012601</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>94</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8999999999999995</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242805</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$58,A9,'Species'!$U$2:$U$58))</x:f>
-        <x:v>74666.85406408244</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8999999999999995</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242805</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>74666.85406408236</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>7.275957614183426e-11</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>9.744561633651903e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>26.65374801</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.0443722736500805</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1107.5727794410382</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>26.65374801</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1108.2847248929302</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$58,A10,'Species'!$U$2:$U$58))</x:f>
-        <x:v>29539.941780628335</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.0443722736500805</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1107.5727794410382</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>29520.965765956742</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>18.976014671592566</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0006427978956391</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0006427978956391562</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>189.735760905</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.496468779737387</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>3136.669635306869</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>189.735760905</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3139.054712628974</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$58,A11,'Species'!$U$2:$U$58))</x:f>
-        <x:v>595590.9344230845</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.496468779737387</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>3136.669635306869</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>595138.3999625577</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>452.53446052677464</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0007603852491374</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0007603852491374195</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4adeb09cf9d49ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1190329112cb4097"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5153,20 +4703,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5174,876 +4714,307 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>880.839083206</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9017962229190166</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>797.620344764003</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>880.839083206</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>835.9420187352314</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$58,A2,'Species'!$U$2:$U$58))</x:f>
-        <x:v>736330.4013961141</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9017962229190166</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>797.620344764003</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>702575.1732283781</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>33755.22816773609</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0480450056506105</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.04804500565061052</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>94.61499204</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>94.61499204</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$58,A3,'Species'!$U$2:$U$58))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>299198.87564510107</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>299198.87564510107</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1267.735760905</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.425086913462429</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2661.2575923971017</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1267.735760905</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2675.0111719168244</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$58,A4,'Species'!$U$2:$U$58))</x:f>
-        <x:v>3391207.3234593514</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.425086913462429</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2661.2575923971017</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3373771.418861748</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>17435.90459760325</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.005168075258485</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0051680752584850045</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>26.65374801</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.0443722736500805</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1107.5727794410382</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>26.65374801</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1108.2847248929302</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$58,A5,'Species'!$U$2:$U$58))</x:f>
-        <x:v>29539.941780628335</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.0443722736500805</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1107.5727794410382</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>29520.965765956742</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>18.976014671592566</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0006427978956391</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0006427978956391562</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1157.6048424599999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.402805045076436</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>252.81628486178803</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1157.6048424599999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>254.69547139719256</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$58,A6,'Species'!$U$2:$U$58))</x:f>
-        <x:v>294836.7110420225</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.402805045076436</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>252.81628486178803</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>292661.3556087526</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2175.3554332699277</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0074330122224202</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.007433012222420218</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>184</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3099999999999996</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>204.17379446695276</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$58,A7,'Species'!$U$2:$U$58))</x:f>
-        <x:v>37567.978181919345</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3099999999999996</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>204.17379446695276</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>37567.97818191931</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3.637978807091713e-11</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>9.683722636004396e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>11727.052717759</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.644703618206624</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>441.2692029217574</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>11727.052717759</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>872.1378151534193</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$58,A8,'Species'!$U$2:$U$58))</x:f>
-        <x:v>10227606.135455301</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.644703618206624</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>441.2692029217574</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>5174787.205386943</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>5052818.930068358</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.9764302819656785</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.9764302819656784</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>15291.294900490002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6041490062793278</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>401.9286887820921</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>15291.294900490002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>475.8501542267673</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$58,A9,'Species'!$U$2:$U$58))</x:f>
-        <x:v>7276365.036725148</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6041490062793278</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>401.9286887820921</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>6146010.109134237</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1130354.9275909103</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1839168676131804</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.18391686761318046</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>12331.921420013</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.64830390351202</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>444.9425131749284</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>12331.921420013</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>787.0683166981489</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$58,A10,'Species'!$U$2:$U$58))</x:f>
-        <x:v>9706064.63370348</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.64830390351202</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>444.9425131749284</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5486996.108896317</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4219068.524807163</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.7689213626316582</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.7689213626316582</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
-        <x:v>1</x:v>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$58,A11,'Species'!$U$2:$U$58))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>637.8022532</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2200000000000006</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>165.9586907437563</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>637.8022532</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>165.95869074375614</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$58,A12,'Species'!$U$2:$U$58))</x:f>
-        <x:v>105848.82689448964</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2200000000000006</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>165.9586907437563</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>105848.82689448976</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>-1.1641532182693481e-10</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>-1.0998262828456073e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>4366.304583254</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.562386056922712</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>365.078331412008</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>4366.304583254</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>401.33599872729906</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$58,A13,'Species'!$U$2:$U$58))</x:f>
-        <x:v>1752355.2106678274</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.562386056922712</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>365.078331412008</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1594043.1916909735</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>158312.01897685393</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0993147612323575</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.09931476123235738</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>16198.782538919999</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.992237983163222</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>98.22860652316866</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>16198.782538919999</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>112.6657266538262</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$58,A14,'Species'!$U$2:$U$58))</x:f>
-        <x:v>1825047.6056547333</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.992237983163222</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>98.22860652316866</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1591183.8361699476</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>233863.76948478562</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.146974701583009</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.14697470158300904</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>555.00000005</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.938828828836141</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>868.6180080353353</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>555.00000005</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>934.0863581368287</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$58,A15,'Species'!$U$2:$U$58))</x:f>
-        <x:v>518417.92881264427</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.938828828836141</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>868.6180080353353</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>482082.994503042</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>36334.93430960225</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0753707032272697</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.07537070322726966</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>463.8561842</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>4.16</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>1445.439770745928</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>463.8561842</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1445.439770745928</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$58,A16,'Species'!$U$2:$U$58))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>670476.1765491288</x:v>
       </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>4.16</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>1445.439770745928</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>670476.1765491288</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G16">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O16">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb6163c00d0f4e7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c16f1f6619b4f6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6218,7 +5189,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6317,7 +5288,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>36870962.78596789</x:v>
+        <x:v>24237547.092674963</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6331,7 +5302,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>36870962.78596789</x:v>
+        <x:v>25986824.216516934</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6345,7 +5316,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-12633415.693292923</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6359,7 +5330,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-10884138.569450952</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6370,9 +5341,9 @@
         <x:v>EEZ_934</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6384,47 +5355,19 @@
         <x:v>EEZ_934</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_934</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_934</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cceb053aeac4a5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R910d0a7a842843f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6471,7 +5414,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
